--- a/human_resources_forms/028_employee_misconduct_termination_documentation_form--human_resources_forms.xlsx
+++ b/human_resources_forms/028_employee_misconduct_termination_documentation_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Termination Date</t>
+          <t>Termination Date End Date</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Termination Date</t>
+          <t>Termination Date Start Date</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>termination_date_end_date</t>
+          <t>termination_date_end_date_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Termination Date</t>
+          <t>Termination Date End Date 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>termination_date_end_date</t>
+          <t>termination_date_end_date_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Termination Date</t>
+          <t>Termination Date End Date 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>reason_for_termination_other</t>
+          <t>reason_for_termination_other_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Reason for Termination</t>
+          <t>Reason For Termination Other 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Termination Date</t>
+          <t>Termination Date Start</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Reason for Termination</t>
+          <t>Reason For Termination Start</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Misconduct Description</t>
+          <t>Misconduct Description Other</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Termination Date</t>
+          <t>Termination Date End</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>supervisor_name</t>
+          <t>supervisor_name_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Supervisor Name</t>
+          <t>Supervisor Name 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Reason for Termination</t>
+          <t>Reason For Termination End</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>manager_name</t>
+          <t>manager_name_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Manager Name</t>
+          <t>Manager Name 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>department_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Department 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
